--- a/output/Data and Chart Outputs/ireland_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/ireland_power_capacity_monthly.xlsx
@@ -164,7 +164,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Ireland installed capacity, month-end: wind (EirGrid series), solar / hydro / bioenergy / storage (registers) (to Mar/26)</a:t>
+              <a:t>Ireland installed capacity, month-end: wind (EirGrid), others (registers) (to Mar/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -412,7 +412,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Ireland net capacity additions per month: wind (EirGrid), solar and batteries (registers) (to Jun/26)</a:t>
+              <a:t>Ireland net additions per month: wind (EirGrid), solar, batteries (registers) (to Jun/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1295,10 +1295,8 @@
           <t>Thu, 01 Oct 2026 14:00:57 GMT</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>621212</t>
-        </is>
+      <c r="D2" t="n">
+        <v>621212</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
